--- a/R_analysis/output/tables/Tabela_Modelos_Multivariados.xlsx
+++ b/R_analysis/output/tables/Tabela_Modelos_Multivariados.xlsx
@@ -413,22 +413,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.1015920015298805</v>
+        <v>0.1015920015298803</v>
       </c>
       <c r="C2">
-        <v>0.04802006971867701</v>
+        <v>0.04802006971867703</v>
       </c>
       <c r="D2">
-        <v>-47.62155668314059</v>
+        <v>-47.62155668314062</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.09232238480554512</v>
+        <v>0.09232238480555448</v>
       </c>
       <c r="G2">
-        <v>0.1118554716329892</v>
+        <v>0.1118554716329608</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -446,19 +446,19 @@
         <v>0.3114295516635247</v>
       </c>
       <c r="C3">
-        <v>0.1148641144465911</v>
+        <v>0.1148641144465912</v>
       </c>
       <c r="D3">
         <v>-10.15619308377006</v>
       </c>
       <c r="E3">
-        <v>3.109829475033584E-24</v>
+        <v>3.109829475033811E-24</v>
       </c>
       <c r="F3">
-        <v>0.2472654722494446</v>
+        <v>0.2472654722494227</v>
       </c>
       <c r="G3">
-        <v>0.3924262629267123</v>
+        <v>0.3924262629265612</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -469,26 +469,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>macrorregiaoNordeste</t>
+          <t>macrorregiaoNorth</t>
         </is>
       </c>
       <c r="B4">
-        <v>0.8614114927791283</v>
+        <v>0.6936278151967542</v>
       </c>
       <c r="C4">
-        <v>0.04188376300249087</v>
+        <v>0.05107002812206946</v>
       </c>
       <c r="D4">
-        <v>-3.561832886531592</v>
+        <v>-7.163100650686006</v>
       </c>
       <c r="E4">
-        <v>0.0003682747802744831</v>
+        <v>7.887239545072161E-13</v>
       </c>
       <c r="F4">
-        <v>0.7937944090530143</v>
+        <v>0.6274432781407536</v>
       </c>
       <c r="G4">
-        <v>0.9341628711081503</v>
+        <v>0.7668526398950377</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -499,26 +499,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>macrorregiaoNorte</t>
+          <t>macrorregiaoNortheast</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.693627815196752</v>
+        <v>0.8614114927791305</v>
       </c>
       <c r="C5">
-        <v>0.05107002812206939</v>
+        <v>0.04188376300249089</v>
       </c>
       <c r="D5">
-        <v>-7.163100650686081</v>
+        <v>-3.561832886531526</v>
       </c>
       <c r="E5">
-        <v>7.887239545067867E-13</v>
+        <v>0.0003682747802745754</v>
       </c>
       <c r="F5">
-        <v>0.6274432781409492</v>
+        <v>0.7937944090531677</v>
       </c>
       <c r="G5">
-        <v>0.7668526398950948</v>
+        <v>0.9341628711082297</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -529,26 +529,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>macrorregiaoSudeste</t>
+          <t>macrorregiaoSouth</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.7462200903713123</v>
+        <v>1.910599671708</v>
       </c>
       <c r="C6">
-        <v>0.03783234385966091</v>
+        <v>0.04020620316559827</v>
       </c>
       <c r="D6">
-        <v>-7.737683292076339</v>
+        <v>16.10241967789329</v>
       </c>
       <c r="E6">
-        <v>1.012446638834882E-14</v>
+        <v>2.45320302719707E-58</v>
       </c>
       <c r="F6">
-        <v>0.6928361451520408</v>
+        <v>1.765953526721596</v>
       </c>
       <c r="G6">
-        <v>0.8030758015353096</v>
+        <v>2.065767327999479</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -559,26 +559,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>macrorregiaoSul</t>
+          <t>macrorregiaoSoutheast</t>
         </is>
       </c>
       <c r="B7">
-        <v>1.910599671707996</v>
+        <v>0.7462200903713143</v>
       </c>
       <c r="C7">
-        <v>0.04020620316559827</v>
+        <v>0.03783234385966094</v>
       </c>
       <c r="D7">
-        <v>16.10241967789323</v>
+        <v>-7.737683292076263</v>
       </c>
       <c r="E7">
-        <v>2.453203027199465E-58</v>
+        <v>1.012446638835483E-14</v>
       </c>
       <c r="F7">
-        <v>1.765953526721479</v>
+        <v>0.692836145152076</v>
       </c>
       <c r="G7">
-        <v>2.065767328000323</v>
+        <v>0.8030758015353334</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>

--- a/R_analysis/output/tables/Tabela_Modelos_Multivariados.xlsx
+++ b/R_analysis/output/tables/Tabela_Modelos_Multivariados.xlsx
@@ -432,7 +432,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Binomial Negativa (IVS geral)</t>
+          <t>Negative Binomial (IVS overall)</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Binomial Negativa (IVS geral)</t>
+          <t>Negative Binomial (IVS overall)</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Binomial Negativa (IVS geral)</t>
+          <t>Negative Binomial (IVS overall)</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Binomial Negativa (IVS geral)</t>
+          <t>Negative Binomial (IVS overall)</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Binomial Negativa (IVS geral)</t>
+          <t>Negative Binomial (IVS overall)</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Binomial Negativa (IVS geral)</t>
+          <t>Negative Binomial (IVS overall)</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>GLMM Multinível</t>
+          <t>GLMM Multilevel</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>GLMM Multinível</t>
+          <t>GLMM Multilevel</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>GLMM Multinível</t>
+          <t>GLMM Multilevel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>GLMM Multinível</t>
+          <t>GLMM Multilevel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
